--- a/docs/cases/主子系统批量建模案例-样例数据.xlsx
+++ b/docs/cases/主子系统批量建模案例-样例数据.xlsx
@@ -38,60 +38,65 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">主系统状态</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t xml:space="preserve">主系统业务部门</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">子系统系统编号</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">子系统英文简称</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">子系统英文名称</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">子系统功能简介</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">子系统重要性等级</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子系统状态</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">子系统业务部门</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">核心功能</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子系统业务部门</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">调整内容</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">业务域</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t xml:space="preserve">应用域</t>
         </is>
@@ -125,60 +130,65 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0001-01</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">CBS-DEP</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">CBS Deposit</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">活期/定期存款、计息与结息。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">存款账户开户、存入、支取、结息</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 年 S1 完成接口改造</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">存款业务域</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -212,60 +222,65 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0001-02</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">CBS-LOAN</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">CBS Loan</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">贷款发放、还款计划与逾期管理。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">授信额度占用、放款、还款、展期</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -299,60 +314,65 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0001-03</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">CBS-GL</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">CBS General Ledger</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">总账、科目与日终轧账。</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t xml:space="preserve">运营管理部</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">记账、科目余额、日终批处理</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -386,60 +406,65 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0002-01</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">MB-ACCT</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mobile Account</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">线上开户与账户管理。</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">三要素核验、开户、账户挂失</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 年 S1 完成接口改造</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -473,60 +498,65 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0002-02</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">MB-TRF</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mobile Transfer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">行内/跨行转账与限额控制。</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">转账、限额校验、收款人管理</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -560,60 +590,65 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0002-03</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">MB-WEALTH</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mobile Wealth</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">理财产品展示、申购与赎回。</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">中</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">个人金融部</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">产品货架、风险测评、申购赎回</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -647,60 +682,65 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t xml:space="preserve">运营管理部</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0003-01</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">ECIF-PARTY</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve">ECIF Party</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">客户身份与证件信息主数据。</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t xml:space="preserve">运营管理部</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">客户主键分配、身份合并、证件有效性</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 年 S1 完成接口改造</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t xml:space="preserve">应用架构-公共服务层</t>
         </is>
@@ -734,60 +774,65 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">运营管理部</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0003-02</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">ECIF-REL</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve">ECIF Relationship</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">客户关系图谱（家庭、企业、担保关系）。</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">中</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">公司金融部</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">关系登记、关系查询、受益所有人穿透</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -821,60 +866,65 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t xml:space="preserve">公司金融部</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0004-01</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">CRM-OPP</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">CRM Opportunity</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">商机与活动管理。</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">中</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">公司金融部</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">商机登记、阶段推进、活动跟踪</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 年 S1 完成接口改造</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -908,60 +958,65 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t xml:space="preserve">公司金融部</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0004-02</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">CRM-VISIT</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">CRM Visit</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">客户拜访与任务派工。</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">低</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">公司金融部</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">拜访计划、任务派工、结果回填</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -995,60 +1050,65 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0005-01</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">RMS-LIMIT</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">RMS Limit</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">统一授信额度管理。</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">额度申请、审批、占用与释放</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 年 S1 完成接口改造</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t xml:space="preserve">风险业务域</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1082,60 +1142,65 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0005-02</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">RMS-COLL</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">RMS Collateral</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">押品登记、估值与权证管理。</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">中</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">押品登记、估值、权证到期提醒</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1169,60 +1234,65 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0006-01</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">AML-SCR</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">AML Screening</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">名单筛查（制裁、黑名单）。</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">名单维护、命中判定、人工复核</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 年 S1 完成接口改造</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1256,60 +1326,65 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0006-02</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">AML-STR</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">AML Suspicious Report</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">可疑交易识别与报送。</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在用</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t xml:space="preserve">风险管理部</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">规则引擎、案例管理、报送接口</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1343,60 +1418,65 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t xml:space="preserve">科技部</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0007-01</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">DH-ING</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">DH Ingestion</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">贴源数据接入与批处理调度。</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">中</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">科技部</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">数据接入、血缘登记、调度编排</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t xml:space="preserve">2026 年 S1 完成接口改造</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t xml:space="preserve">应用架构-公共服务层</t>
         </is>
@@ -1430,60 +1510,65 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t xml:space="preserve">科技部</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">SYS-0007-02</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">DH-SVC</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">DH Service</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">数据服务与指标 API。</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">中</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在建</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">科技部</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">指标定义、API 发布、调用审计</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1517,14 +1602,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t xml:space="preserve">下线</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t xml:space="preserve">运营管理部</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -1571,6 +1656,11 @@
         </is>
       </c>
       <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/docs/cases/主子系统批量建模案例-样例数据.xlsx
+++ b/docs/cases/主子系统批量建模案例-样例数据.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="157">
   <si>
     <t>主系统</t>
   </si>
@@ -89,12 +89,15 @@
     <t>应用域</t>
   </si>
   <si>
+    <t>核心</t>
+  </si>
+  <si>
+    <t>SYS-0001</t>
+  </si>
+  <si>
     <t>CBS</t>
   </si>
   <si>
-    <t>SYS-0001</t>
-  </si>
-  <si>
     <t>Core Banking System</t>
   </si>
   <si>
@@ -110,12 +113,15 @@
     <t>个人金融部</t>
   </si>
   <si>
+    <t>核心存款</t>
+  </si>
+  <si>
+    <t>SYS-0001-01</t>
+  </si>
+  <si>
     <t>CBS-DEP</t>
   </si>
   <si>
-    <t>SYS-0001-01</t>
-  </si>
-  <si>
     <t>CBS Deposit</t>
   </si>
   <si>
@@ -173,10 +179,13 @@
     <t>记账、科目余额、日终批处理</t>
   </si>
   <si>
+    <t>移动银行</t>
+  </si>
+  <si>
+    <t>SYS-0002</t>
+  </si>
+  <si>
     <t>MBANK</t>
-  </si>
-  <si>
-    <t>SYS-0002</t>
   </si>
   <si>
     <t>Mobile Banking</t>
@@ -1718,58 +1727,58 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" t="s">
-        <v>26</v>
-      </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -1780,58 +1789,58 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -1842,923 +1851,923 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="R7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" t="s">
         <v>69</v>
       </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M9" t="s">
-        <v>81</v>
-      </c>
-      <c r="N9" t="s">
-        <v>66</v>
-      </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
         <v>85</v>
       </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>82</v>
-      </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="N10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="R10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" t="s">
         <v>85</v>
       </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" t="s">
-        <v>82</v>
-      </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="R11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s">
+        <v>111</v>
+      </c>
+      <c r="M12" t="s">
+        <v>112</v>
+      </c>
+      <c r="N12" t="s">
+        <v>33</v>
+      </c>
+      <c r="O12" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" t="s">
         <v>108</v>
       </c>
-      <c r="M12" t="s">
-        <v>109</v>
-      </c>
-      <c r="N12" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" t="s">
-        <v>105</v>
-      </c>
       <c r="Q12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="R12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="T12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="R13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P14" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="R14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M15" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="R15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" t="s">
+        <v>142</v>
+      </c>
+      <c r="J16" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" t="s">
+        <v>142</v>
+      </c>
+      <c r="L16" t="s">
+        <v>144</v>
+      </c>
+      <c r="M16" t="s">
+        <v>145</v>
+      </c>
+      <c r="N16" t="s">
+        <v>69</v>
+      </c>
+      <c r="O16" t="s">
         <v>134</v>
       </c>
-      <c r="C16" t="s">
-        <v>133</v>
-      </c>
-      <c r="D16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16" t="s">
-        <v>137</v>
-      </c>
-      <c r="G16" t="s">
-        <v>104</v>
-      </c>
-      <c r="H16" t="s">
-        <v>138</v>
-      </c>
-      <c r="I16" t="s">
-        <v>139</v>
-      </c>
-      <c r="J16" t="s">
-        <v>140</v>
-      </c>
-      <c r="K16" t="s">
-        <v>139</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="P16" t="s">
         <v>141</v>
       </c>
-      <c r="M16" t="s">
-        <v>142</v>
-      </c>
-      <c r="N16" t="s">
-        <v>66</v>
-      </c>
-      <c r="O16" t="s">
-        <v>131</v>
-      </c>
-      <c r="P16" t="s">
-        <v>138</v>
-      </c>
       <c r="Q16" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="R16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" t="s">
+        <v>147</v>
+      </c>
+      <c r="J17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L17" t="s">
+        <v>149</v>
+      </c>
+      <c r="M17" t="s">
+        <v>150</v>
+      </c>
+      <c r="N17" t="s">
+        <v>69</v>
+      </c>
+      <c r="O17" t="s">
         <v>134</v>
       </c>
-      <c r="C17" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F17" t="s">
-        <v>137</v>
-      </c>
-      <c r="G17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H17" t="s">
-        <v>138</v>
-      </c>
-      <c r="I17" t="s">
-        <v>144</v>
-      </c>
-      <c r="J17" t="s">
-        <v>145</v>
-      </c>
-      <c r="K17" t="s">
-        <v>144</v>
-      </c>
-      <c r="L17" t="s">
-        <v>146</v>
-      </c>
-      <c r="M17" t="s">
-        <v>147</v>
-      </c>
-      <c r="N17" t="s">
-        <v>66</v>
-      </c>
-      <c r="O17" t="s">
-        <v>131</v>
-      </c>
       <c r="P17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="R17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D18" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G18" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
